--- a/data/WP18/WP18_sachgebiete_SPD.xlsx
+++ b/data/WP18/WP18_sachgebiete_SPD.xlsx
@@ -3446,13 +3446,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C12A59CA-DA5B-4919-8D52-34C0ADD2560F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{847A57F8-AD46-4485-B0CF-709DE964E594}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50091E54-0197-4088-B73B-558C5784B223}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45A0B281-A089-46FC-A2A3-3E83D3596EAC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49C7FA8F-842E-478B-81B8-1FE4C6D782BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0011FFBE-BD41-48BA-8CE2-7C6F3005B782}"/>
 </file>
--- a/data/WP18/WP18_sachgebiete_SPD.xlsx
+++ b/data/WP18/WP18_sachgebiete_SPD.xlsx
@@ -446,7 +446,7 @@
         <v>37.632183908046</v>
       </c>
       <c r="E2" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         <v>37.6009389671362</v>
       </c>
       <c r="E3" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         <v>31.347619047619</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         <v>36.815</v>
       </c>
       <c r="E5" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>30.2538461538462</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>40.325</v>
       </c>
       <c r="E7" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -548,7 +548,7 @@
         <v>31.5042016806723</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +565,7 @@
         <v>30.7456140350877</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
         <v>36.3245614035088</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>29.3272727272727</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -616,7 +616,7 @@
         <v>40.9519230769231</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +633,7 @@
         <v>29.2207792207792</v>
       </c>
       <c r="E13" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +650,7 @@
         <v>36.8051948051948</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         <v>34.6849315068493</v>
       </c>
       <c r="E15" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -684,7 +684,7 @@
         <v>38.830985915493</v>
       </c>
       <c r="E16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -701,7 +701,7 @@
         <v>31.7857142857143</v>
       </c>
       <c r="E17" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
@@ -718,7 +718,7 @@
         <v>37.5285714285714</v>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>28.8382352941176</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -752,7 +752,7 @@
         <v>36.8095238095238</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
@@ -1006,13 +1006,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3002A21-62C6-4331-BBBA-09920729B244}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75E504D2-B193-4D06-884B-93279240DF82}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A742208-A78D-4C5F-BEEE-AC0E7497CAA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B51A000-C663-4881-A2F8-B42532D9BC5B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C510ED-7EFA-428F-9E3E-D90D6B303694}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96226947-52B3-41E1-BBE1-1852B0F319B8}"/>
 </file>